--- a/testdata/configurationTST/execute.xlsx
+++ b/testdata/configurationTST/execute.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="13560" windowHeight="5976"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$147</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="310">
   <si>
     <t>App</t>
   </si>
@@ -937,6 +937,24 @@
   </si>
   <si>
     <t>C70923</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD_Statemants_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70924</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Statemants_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70925</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Statemants_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70926</t>
   </si>
   <si>
     <t>Automated Test Names</t>
@@ -1635,7 +1653,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1655,6 +1673,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5336,28 +5357,73 @@
       </c>
     </row>
     <row r="146" customFormat="1" spans="1:7">
-      <c r="A146" s="6"/>
-      <c r="B146" s="6"/>
-      <c r="C146" s="6"/>
-      <c r="D146" s="6"/>
-      <c r="E146" s="6"/>
-      <c r="F146" s="8"/>
-    </row>
-    <row r="147" customFormat="1" ht="15.15" spans="1:7">
-      <c r="A147" s="6"/>
-      <c r="B147" s="6"/>
-      <c r="C147" s="6"/>
-      <c r="D147" s="6"/>
-      <c r="E147" s="6"/>
-      <c r="F147" s="8"/>
+      <c r="A146" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G146" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" customFormat="1" spans="1:7">
+      <c r="A147" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G147" s="9" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="148" customFormat="1" ht="15.15" spans="1:7">
-      <c r="A148" s="6"/>
-      <c r="B148" s="3"/>
-      <c r="C148" s="6"/>
-      <c r="D148" s="6"/>
-      <c r="E148" s="6"/>
-      <c r="F148" s="8"/>
+      <c r="A148" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G148" s="9" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="149" customFormat="1" ht="15.15" spans="1:7">
       <c r="A149" s="6"/>
@@ -5568,7 +5634,7 @@
       <c r="B194" s="3"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G145" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G147" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C$1:C$1048576">
@@ -5596,7 +5662,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -5708,7 +5774,7 @@
     </row>
     <row r="15" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
